--- a/weekly_hours_report.xlsx
+++ b/weekly_hours_report.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="League of Legends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overwatch 2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +28,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +54,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -629,12 +638,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No games played</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.00</t>
+          <t>League of Legends, Overwatch 2</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>1.00, 2.00</t>
         </is>
       </c>
     </row>
@@ -996,6 +1005,94 @@
         <is>
           <t>0.00</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UserID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flurpish</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.203397674912973e+17</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>UserID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flurpish</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.203397674912973e+17</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
